--- a/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TEST_DESIGN.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TEST_DESIGN.xlsx
@@ -447,7 +447,7 @@
         <v>Trong kiểm thử phần mềm, sự khác biệt cơ bản giữa Mức độ nghiêm trọng (Severity) và Mức độ ưu tiên (Priority) của lỗi là gì?</v>
       </c>
       <c r="C2" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D2" t="str">
         <v>Severity phản ánh tính chất kỹ thuật và tác động lỗi lên hệ thống (ví dụ: sập nguồn, mất dữ liệu -&gt; High). Priority phản ánh góc độ quản lý và kinh doanh (cần sửa sớm hay muộn).</v>
@@ -476,7 +476,7 @@
         <v>Kỹ thuật thiết kế kiểm thử "Phân vùng tương đương" (Equivalence Partitioning) hoạt động theo nguyên lý nào?</v>
       </c>
       <c r="C3" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D3" t="str">
         <v>Phân vùng tương đương giúp giảm thiểu số lượng test case bằng cách chọn ra các giá trị đại diện đại diện cho từng nhóm giá trị có cùng logic xử lý.</v>
@@ -505,7 +505,7 @@
         <v>Kỹ thuật "Phân tích giá trị biên" (Boundary Value Analysis) khuyên kiểm thử viên tập trung thiết kế các ca kiểm thử ở vị trí nào?</v>
       </c>
       <c r="C4" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D4" t="str">
         <v>Lập trình viên thường viết sai các toán tử so sánh biên (e.g. dùng `&lt;` thay vì `&lt;=`), do đó việc test các giá trị biên mang lại hiệu quả phát hiện lỗi cao nhất.</v>
@@ -534,7 +534,7 @@
         <v>Một Bug Report chuẩn chất lượng bắt buộc phải bao gồm những thông tin cốt lõi nào để lập trình viên có thể sửa lỗi?</v>
       </c>
       <c r="C5" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D5" t="str">
         <v>Bug Report cần cung cấp đầy đủ thông tin khách quan (Steps, Actual, Expected, Environment) giúp dev tái hiện lại được lỗi một cách nhanh nhất.</v>
@@ -563,7 +563,7 @@
         <v>Quy trình kiểm thử phần mềm (STLC - Software Testing Life Cycle) thường bắt đầu bằng giai đoạn nào?</v>
       </c>
       <c r="C6" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D6" t="str">
         <v>STLC bắt đầu bằng việc phân tích yêu cầu để hiểu rõ hệ thống hoạt động thế nào, từ đó lập kế hoạch và thiết kế kịch bản test chính xác.</v>
@@ -592,7 +592,7 @@
         <v>Kiểm thử hồi quy (Regression Testing) được thực hiện nhằm mục đích chính là gì?</v>
       </c>
       <c r="C7" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D7" t="str">
         <v>Kiểm thử hồi quy đảm bảo tính ổn định của phần mềm. Mỗi khi code thay đổi, ta chạy lại một bộ test case lõi để đảm bảo không có tác dụng phụ làm hỏng tính năng cũ.</v>
@@ -621,7 +621,7 @@
         <v>Trạng thái cơ bản của một lỗi trong vòng đời của Bug (Bug Lifecycle) đi theo tiến trình chuẩn nào dưới đây?</v>
       </c>
       <c r="C8" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D8" t="str">
         <v>Tiến trình chuẩn bắt đầu từ việc phát hiện lỗi (New), gán cho dev (Assigned), dev xác nhận sửa (Open/Resolved), QA kiểm tra lại đạt yêu cầu thì đóng lỗi (Closed).</v>
@@ -650,7 +650,7 @@
         <v>Định nghĩa nào đúng về kiểm thử "Hộp đen" (Black-box Testing)?</v>
       </c>
       <c r="C9" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D9" t="str">
         <v>Kiểm thử hộp đen coi phần mềm như một hộp đen không thấy bên trong, chỉ tập trung vào hành vi chức năng từ góc nhìn của người dùng.</v>
@@ -679,7 +679,7 @@
         <v>Yêu cầu kiểm thử một form đăng ký có trường nhập "Mật khẩu" quy định độ dài từ 8 đến 16 ký tự. Sử dụng kỹ thuật Phân tích giá trị biên (BVA), bộ giá trị kiểm thử nào sau đây là tối ưu nhất?</v>
       </c>
       <c r="C10" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D10" t="str">
         <v>Bộ BVA chuẩn cho khoảng [Min, Max] là: Min-1 (7), Min (8), Min+1 (9) và Max-1 (15), Max (16), Max+1 (17) để bao phủ đầy đủ các điểm ranh giới.</v>
@@ -708,7 +708,7 @@
         <v>Khi dev báo cáo đã sửa xong một lỗi (status Resolved) và gửi lại bản build, quy trình re-test lỗi đó của QA diễn ra như thế nào?</v>
       </c>
       <c r="C11" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D11" t="str">
         <v>QA bắt buộc phải re-test trên bản build mới để xác minh bug thực sự đã được sửa, sau đó cập nhật trạng thái lỗi (Closed hoặc Reopen) tương ứng.</v>
@@ -737,7 +737,7 @@
         <v>Trong thiết kế test case bằng Kỹ thuật "Bảng quyết định" (Decision Table Testing), khi nào kỹ thuật này mang lại hiệu quả cao nhất?</v>
       </c>
       <c r="C12" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D12" t="str">
         <v>Bảng quyết định giúp hệ thống hóa các tổ hợp logic (T/F của các điều kiện) một cách đầy đủ, tránh bỏ sót các trường hợp nghiệp vụ phức tạp đan xen.</v>
@@ -766,7 +766,7 @@
         <v>Sự khác biệt chính giữa kiểm thử "Sanity Testing" và kiểm thử "Regression Testing" là gì?</v>
       </c>
       <c r="C13" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D13" t="str">
         <v>Sanity testing là tập con của Regression testing, dùng để xác minh nhanh xem thay đổi/sửa lỗi cụ thể có hoạt động đúng logic hay không trước khi chạy hồi quy diện rộng.</v>
@@ -795,7 +795,7 @@
         <v>Lỗi phát sinh: Ứng dụng crash (sập) ngay lập tức khi người dùng click vào nút thanh toán, không thể thực hiện được giao dịch. BA/QA đánh giá độ nghiêm trọng (Severity) và độ ưu tiên (Priority) của lỗi này thế nào?</v>
       </c>
       <c r="C14" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D14" t="str">
         <v>Lỗi crash tính năng chính (thanh toán) vi phạm nặng nề trải nghiệm người dùng và quy trình nghiệp vụ cốt lõi, do đó cần xếp vào Severity Critical và Priority High (sửa ngay lập tức).</v>
@@ -824,7 +824,7 @@
         <v>Quy trình kiểm thử "State Transition Testing" (Kiểm thử chuyển trạng thái) áp dụng tốt nhất cho loại hệ thống nào?</v>
       </c>
       <c r="C15" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D15" t="str">
         <v>Kiểm thử chuyển trạng thái giúp bao phủ đầy đủ các luồng chuyển dịch trạng thái hợp lệ và phát hiện các luồng chuyển dịch sai logic (ví dụ: Đơn hàng đã hủy không được phép chuyển sang Đang giao).</v>
@@ -853,7 +853,7 @@
         <v>Khái niệm "Exploratory Testing" (Kiểm thử khám phá) khác gì so với kiểm thử dựa trên kịch bản (Scripted Testing) thông thường?</v>
       </c>
       <c r="C16" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D16" t="str">
         <v>Exploratory testing phát huy tính sáng tạo và kinh nghiệm của QA để tìm ra các bug sâu, góc khuất ngoài kịch bản chuẩn, thường thực hiện sau khi đã chạy hết test case chuẩn.</v>
@@ -882,7 +882,7 @@
         <v>Trong bối cảnh Agile, hoạt động kiểm thử nên được bắt đầu vào thời điểm nào để tối ưu hóa chất lượng dự án?</v>
       </c>
       <c r="C17" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D17" t="str">
         <v>Nguyên lý "Kiểm thử sớm" (Early Testing) giúp giảm thiểu chi phí sửa lỗi. Phát hiện lỗi logic trên tài liệu yêu cầu (SRS) rẻ hơn gấp hàng chục lần so với sửa lỗi sau khi dev đã code xong.</v>
@@ -911,7 +911,7 @@
         <v>Khi viết kịch bản kiểm thử (Test Case), tại sao việc quy định rõ "Expected Result" (Kết quả mong đợi) là bắt buộc?</v>
       </c>
       <c r="C18" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D18" t="str">
         <v>Expected Result là tiêu chuẩn nghiệm nghiệm thu. Không có kết quả mong đợi rõ ràng, QA sẽ không thể đánh giá chính xác hành vi hệ thống là đúng hay sai.</v>
@@ -940,7 +940,7 @@
         <v>Chức năng: Chọn ngày đặt phòng khách sạn. Điều kiện: `Ngày đến` và `Ngày đi` phải hợp lệ (Ngày đi sau Ngày đến và cả hai phải lớn hơn hoặc bằng Ngày hiện tại). Hãy thiết kế các ca kiểm thử biên (BVA) cho điều kiện này.</v>
       </c>
       <c r="C19" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D19" t="str">
         <v>Kiểm thử biên cho mối quan hệ ngày tháng đòi hỏi so khớp khoảng thời gian tối thiểu (0 ngày, 1 ngày) và mốc thời gian so với hiện tại để phát hiện lỗi so sánh thời gian.</v>
@@ -969,7 +969,7 @@
         <v>Trong một dự án Agile, Sprint chỉ kéo dài 2 tuần. Lập trình viên bàn giao tính năng muộn vào ngày cuối cùng của Sprint. QA nên giải quyết tình huống này thế nào để đảm bảo chất lượng?</v>
       </c>
       <c r="C20" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D20" t="str">
         <v>QA cần chủ động quản lý rủi ro bằng cách kiểm thử dựa trên độ ưu tiên (Risk-based testing), tập trung vào Happy Path và Core flows để đảm bảo chất lượng tối thiểu trước khi release.</v>
@@ -998,7 +998,7 @@
         <v>Hệ thống thương mại điện tử có luật: "Nếu giỏ hàng &gt;= 1 triệu VND và khách hàng là VIP, giảm giá 10%. Nếu có mã KM thêm, giảm thêm 5% tổng đơn". Thiết kế test case bằng Decision Table thế nào để bao phủ tối ưu?</v>
       </c>
       <c r="C21" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D21" t="str">
         <v>Decision Table cho 3 điều kiện nhị phân (T/F) sẽ có 8 tổ hợp quy tắc. Việc kiểm thử đầy đủ 8 trường hợp này đảm bảo hệ thống không bị lỗi logic chéo khi tính toán giá tiền đơn hàng.</v>
@@ -1027,7 +1027,7 @@
         <v>Hiện tượng "Pesticide Paradox" (Nghịch lý thuốc trừ sâu) trong kiểm thử phần mềm phát biểu điều gì và QA khắc phục bằng cách nào?</v>
       </c>
       <c r="C22" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D22" t="str">
         <v>Nghịch lý thuốc trừ sâu xảy ra vì phần mềm tiến hóa và các bug cũ đã được sửa. QA cần cập nhật kịch bản test để thích ứng với các thay đổi nghiệp vụ và kỹ thuật mới.</v>
@@ -1056,7 +1056,7 @@
         <v>Khi thực hiện kiểm thử một hệ thống tích hợp lớn (System Integration Testing - SIT), QA phát hiện ra một bug nghiêm trọng nhưng không thể xác định lỗi nằm ở service của Backend tự viết hay ở API của bên thứ ba (Third-party). QA xử lý thế nào?</v>
       </c>
       <c r="C23" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D23" t="str">
         <v>QA kỹ thuật cần phân tích log (Request payload gửi đi có đúng đặc tả? Response code trả về là gì? 4xx hay 5xx?). Việc xác định đúng lỗi giúp đẩy nhanh tiến độ sửa lỗi và gán đúng đối tượng xử lý.</v>
@@ -1085,7 +1085,7 @@
         <v>Trong kiểm thử tự động, khái niệm "Flaky Test" nghĩa là gì và gây tác hại như thế nào?</v>
       </c>
       <c r="C24" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D24" t="str">
         <v>Flaky Tests thường do bất đồng bộ (timing issues), dữ liệu test không ổn định, hoặc môi trường mạng chập chờn. Nó làm giảm giá trị của CI/CD vì kết quả không đáng tin cậy.</v>
@@ -1114,7 +1114,7 @@
         <v>Khi viết Test Plan cho một dự án di động lớn, yếu tố "Suspension Criteria" (Tiêu chí tạm dừng kiểm thử) quy định điều gì?</v>
       </c>
       <c r="C25" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D25" t="str">
         <v>Suspension Criteria giúp bảo vệ tài nguyên dự án. Nếu bản build quá lỗi (blocker/crash liên tục), việc cố gắng test tiếp sẽ vô ích và lãng phí thời gian của QA.</v>
@@ -1143,7 +1143,7 @@
         <v>Quy trình kiểm thử "State Transition" có 1 kịch bản: Nhập sai PIN 1 lần (trạng thái: Active) -&gt; Nhập sai lần 2 (Active) -&gt; Nhập sai lần 3 (Blocked). QA cần thiết kế tối thiểu bao nhiêu test case để kiểm tra luồng chuyển trạng thái này?</v>
       </c>
       <c r="C26" t="str">
-        <v>Tester Methodology</v>
+        <v>Tester Design Techniques</v>
       </c>
       <c r="D26" t="str">
         <v>Để kiểm tra tính đúng đắn của máy trạng thái (State Machine), ta cần kiểm tra từng bước chuyển: (Active + Sai 1 -&gt; Active), (Active + Sai 2 -&gt; Active), (Active + Sai 3 -&gt; Blocked) để đảm bảo bộ đếm hoạt động chính xác.</v>

--- a/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TEST_DESIGN.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Manual/multiple_choice_sample_template_TEST_DESIGN.xlsx
@@ -453,19 +453,19 @@
         <v>Severity phản ánh tính chất kỹ thuật và tác động lỗi lên hệ thống (ví dụ: sập nguồn, mất dữ liệu -&gt; High). Priority phản ánh góc độ quản lý và kinh doanh (cần sửa sớm hay muộn).</v>
       </c>
       <c r="E2" t="str">
-        <v>Severity đo lường mức độ ảnh hưởng của lỗi đối với vận hành hệ thống; Priority đo lường mức độ khẩn cấp cần sửa lỗi theo kế hoạch kinh doanh</v>
+        <v>Severity đo lường số dòng code bị lỗi; Priority đo lường thời gian cần thiết để sửa xong lỗi đó</v>
       </c>
       <c r="F2" t="str">
         <v>Severity do khách hàng đánh giá; Priority do kiểm thử viên tự ý quyết định và phân bổ</v>
       </c>
       <c r="G2" t="str">
+        <v>Severity đo lường mức độ ảnh hưởng của lỗi đối với vận hành hệ thống; Priority đo lường mức độ khẩn cấp cần sửa lỗi theo kế hoạch kinh doanh</v>
+      </c>
+      <c r="H2" t="str">
         <v>Severity chỉ áp dụng cho kiểm thử tự động; Priority chỉ áp dụng cho kiểm thử thủ công</v>
       </c>
-      <c r="H2" t="str">
-        <v>Severity đo lường số dòng code bị lỗi; Priority đo lường thời gian cần thiết để sửa xong lỗi đó</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -488,10 +488,10 @@
         <v>Kiểm thử toàn bộ tất cả các giá trị có thể nhập vào hệ thống để đảm bảo không bỏ sót bất kỳ lỗi nào</v>
       </c>
       <c r="G3" t="str">
+        <v>Phân chia đội ngũ kiểm thử thành các nhóm độc lập để kiểm tra chéo công việc của nhau</v>
+      </c>
+      <c r="H3" t="str">
         <v>Chia nhỏ giao diện phần mềm thành các khối có kích thước và màu sắc tương đồng nhau để thiết kế test case</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Phân chia đội ngũ kiểm thử thành các nhóm độc lập để kiểm tra chéo công việc của nhau</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -511,19 +511,19 @@
         <v>Lập trình viên thường viết sai các toán tử so sánh biên (e.g. dùng `&lt;` thay vì `&lt;=`), do đó việc test các giá trị biên mang lại hiệu quả phát hiện lỗi cao nhất.</v>
       </c>
       <c r="E4" t="str">
+        <v>Tại các giao diện hiển thị ở rìa màn hình điện thoại hoặc máy tính</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Tại các thời điểm bắt đầu và kết thúc ca làm việc của đội phát triển</v>
+      </c>
+      <c r="G4" t="str">
         <v>Tại các giá trị biên (ngay biên, sát dưới biên, sát trên biên) của các phân vùng dữ liệu đầu vào — nơi thường xảy ra lỗi logic lập trình</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>Tại các giá trị nằm chính giữa các phân vùng dữ liệu hợp lệ và không hợp lệ</v>
       </c>
-      <c r="G4" t="str">
-        <v>Tại các giao diện hiển thị ở rìa màn hình điện thoại hoặc máy tính</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Tại các thời điểm bắt đầu và kết thúc ca làm việc của đội phát triển</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Bug Report cần cung cấp đầy đủ thông tin khách quan (Steps, Actual, Expected, Environment) giúp dev tái hiện lại được lỗi một cách nhanh nhất.</v>
       </c>
       <c r="E5" t="str">
+        <v>Đoạn code sửa lỗi mẫu do chính kiểm thử viên tự viết và tối ưu hóa</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Danh sách tất cả các test case đã chạy thành công trước khi phát hiện ra lỗi này</v>
+      </c>
+      <c r="G5" t="str">
         <v>Tiêu đề Bug, Các bước tái hiện (Steps to reproduce), Kết quả thực tế (Actual result), Kết quả mong đợi (Expected result) và Môi trường test</v>
       </c>
-      <c r="F5" t="str">
-        <v>Đoạn code sửa lỗi mẫu do chính kiểm thử viên tự viết và tối ưu hóa</v>
-      </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Ý kiến đánh giá chủ quan của kiểm thử viên về năng lực của lập trình viên viết tính năng đó</v>
       </c>
-      <c r="H5" t="str">
-        <v>Danh sách tất cả các test case đã chạy thành công trước khi phát hiện ra lỗi này</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>STLC bắt đầu bằng việc phân tích yêu cầu để hiểu rõ hệ thống hoạt động thế nào, từ đó lập kế hoạch và thiết kế kịch bản test chính xác.</v>
       </c>
       <c r="E6" t="str">
-        <v>Phân tích yêu cầu (Requirement Analysis) — tìm hiểu nghiệp vụ và xác định các tính năng có thể kiểm thử</v>
+        <v>Thiết lập môi trường kiểm thử (Test Environment Setup) — cài đặt cơ sở dữ liệu và máy chủ</v>
       </c>
       <c r="F6" t="str">
         <v>Thiết kế ca kiểm thử (Test Case Design) — viết tài liệu các bước chạy thử phần mềm</v>
       </c>
       <c r="G6" t="str">
+        <v>Phân tích yêu cầu (Requirement Analysis) — tìm hiểu nghiệp vụ và xác định các tính năng có thể kiểm thử</v>
+      </c>
+      <c r="H6" t="str">
         <v>Thực hiện kiểm thử (Test Execution) — mở ứng dụng chạy thử và tìm lỗi</v>
       </c>
-      <c r="H6" t="str">
-        <v>Thiết lập môi trường kiểm thử (Test Environment Setup) — cài đặt cơ sở dữ liệu và máy chủ</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Kiểm thử hồi quy đảm bảo tính ổn định của phần mềm. Mỗi khi code thay đổi, ta chạy lại một bộ test case lõi để đảm bảo không có tác dụng phụ làm hỏng tính năng cũ.</v>
       </c>
       <c r="E7" t="str">
+        <v>Kiểm tra xem hệ thống có chạy tốt trên các dòng điện thoại đời cũ hay không</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Đo lường thời gian tải trang tối đa của hệ thống khi có 1000 người dùng truy cập</v>
+      </c>
+      <c r="G7" t="str">
         <v>Xác minh rằng các thay đổi mới trong code (sửa bug, tính năng mới) không làm ảnh hưởng hoặc gây lỗi cho các chức năng hiện có đang chạy ổn định</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Kiểm tra xem hệ thống có chạy tốt trên các dòng điện thoại đời cũ hay không</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Đo lường thời gian tải trang tối đa của hệ thống khi có 1000 người dùng truy cập</v>
       </c>
       <c r="H7" t="str">
         <v>Tạo ra bản sao lưu tự động của cơ sở dữ liệu trước khi bàn giao cho khách hàng</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Tiến trình chuẩn bắt đầu từ việc phát hiện lỗi (New), gán cho dev (Assigned), dev xác nhận sửa (Open/Resolved), QA kiểm tra lại đạt yêu cầu thì đóng lỗi (Closed).</v>
       </c>
       <c r="E8" t="str">
+        <v>Assigned (Giao cho dev) → Resolved (Đã sửa xong) → New (Tạo lỗi mới) → Closed (Đóng lỗi)</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Open (Đang sửa) → New (Tạo mới) → Reopened (Mở lại) → Verified (Đã xác nhận)</v>
+      </c>
+      <c r="G8" t="str">
         <v>New (Mới phát hiện) → Assigned (Giao cho dev) → Open (Đang sửa) → Resolved (Đã sửa xong) → Closed (Đã re-test và đóng lỗi)</v>
       </c>
-      <c r="F8" t="str">
+      <c r="H8" t="str">
         <v>New (Mới phát hiện) → Closed (Đóng lỗi ngay) → Open (Mở lại) → Resolved (Đã sửa xong)</v>
       </c>
-      <c r="G8" t="str">
-        <v>Assigned (Giao cho dev) → Resolved (Đã sửa xong) → New (Tạo lỗi mới) → Closed (Đóng lỗi)</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Open (Đang sửa) → New (Tạo mới) → Reopened (Mở lại) → Verified (Đã xác nhận)</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>Kiểm thử hộp đen coi phần mềm như một hộp đen không thấy bên trong, chỉ tập trung vào hành vi chức năng từ góc nhìn của người dùng.</v>
       </c>
       <c r="E9" t="str">
+        <v>Kiểm thử hệ thống trong phòng tối không có ánh sáng để kiểm tra độ sáng màn hình ứng dụng di động</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Kiểm thử bảo mật chống lại các cuộc tấn công mạng từ các tin tặc bên ngoài internet</v>
+      </c>
+      <c r="G9" t="str">
         <v>Kiểm thử chức năng dựa trên yêu cầu đầu vào và đầu ra của hệ thống mà không cần biết cấu trúc mã nguồn bên trong</v>
       </c>
-      <c r="F9" t="str">
+      <c r="H9" t="str">
         <v>Kiểm thử cấu trúc mã nguồn bên trong hệ thống đòi hỏi khả năng đọc hiểu code của lập trình viên</v>
       </c>
-      <c r="G9" t="str">
-        <v>Kiểm thử hệ thống trong phòng tối không có ánh sáng để kiểm tra độ sáng màn hình ứng dụng di động</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Kiểm thử bảo mật chống lại các cuộc tấn công mạng từ các tin tặc bên ngoài internet</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -691,10 +691,10 @@
         <v>8, 12, 16 ký tự — kiểm tra giá trị tối thiểu, trung bình và tối đa</v>
       </c>
       <c r="G10" t="str">
+        <v>7, 8, 16, 17 ký tự — kiểm tra các giá trị ngay trên biên và ngay dưới biên</v>
+      </c>
+      <c r="H10" t="str">
         <v>0, 8, 16, 100 ký tự — kiểm tra các giá trị cực trị ngẫu nhiên rộng</v>
-      </c>
-      <c r="H10" t="str">
-        <v>7, 8, 16, 17 ký tự — kiểm tra các giá trị ngay trên biên và ngay dưới biên</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -714,19 +714,19 @@
         <v>QA bắt buộc phải re-test trên bản build mới để xác minh bug thực sự đã được sửa, sau đó cập nhật trạng thái lỗi (Closed hoặc Reopen) tương ứng.</v>
       </c>
       <c r="E11" t="str">
-        <v>Chạy lại đúng các bước trong Bug Report trên bản build mới; nếu lỗi không còn thì đóng bug (Closed), nếu lỗi vẫn còn thì mở lại (Reopened)</v>
+        <v>Chạy lại toàn bộ kịch bản kiểm thử hiệu năng của hệ thống để xác thực tốc độ xử lý</v>
       </c>
       <c r="F11" t="str">
         <v>Đóng ngay lỗi đó trên hệ thống vì dev đã xác nhận sửa xong trong code</v>
       </c>
       <c r="G11" t="str">
+        <v>Chạy lại đúng các bước trong Bug Report trên bản build mới; nếu lỗi không còn thì đóng bug (Closed), nếu lỗi vẫn còn thì mở lại (Reopened)</v>
+      </c>
+      <c r="H11" t="str">
         <v>Viết một test case hoàn toàn mới để kiểm tra một tính năng khác của hệ thống</v>
       </c>
-      <c r="H11" t="str">
-        <v>Chạy lại toàn bộ kịch bản kiểm thử hiệu năng của hệ thống để xác thực tốc độ xử lý</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -749,10 +749,10 @@
         <v>Khi cần kiểm thử hiệu năng tải trang web dưới tác động của hàng ngàn request cùng lúc</v>
       </c>
       <c r="G12" t="str">
+        <v>Khi cần thiết kế các kịch bản kiểm thử tự động cho luồng thanh toán API</v>
+      </c>
+      <c r="H12" t="str">
         <v>Khi cần kiểm tra khả năng tương thích của ứng dụng trên nhiều phiên bản hệ điều hành Android</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Khi cần thiết kế các kịch bản kiểm thử tự động cho luồng thanh toán API</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -775,13 +775,13 @@
         <v>Sanity test là kiểm tra nhanh, tập trung hẹp vào một chức năng vừa được sửa đổi; Regression test là kiểm tra rộng, bao quát toàn bộ hệ thống để phát hiện lỗi hồi quy</v>
       </c>
       <c r="F13" t="str">
+        <v>Sanity test chỉ chạy được trên môi trường Production; Regression test chỉ chạy trên Local</v>
+      </c>
+      <c r="G13" t="str">
         <v>Sanity test do lập trình viên tự chạy; Regression test do kiểm thử viên chạy thủ công</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Sanity test kiểm tra tính tương thích; Regression test kiểm tra tính hiệu năng hệ thống</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Sanity test chỉ chạy được trên môi trường Production; Regression test chỉ chạy trên Local</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -801,19 +801,19 @@
         <v>Lỗi crash tính năng chính (thanh toán) vi phạm nặng nề trải nghiệm người dùng và quy trình nghiệp vụ cốt lõi, do đó cần xếp vào Severity Critical và Priority High (sửa ngay lập tức).</v>
       </c>
       <c r="E14" t="str">
+        <v>Severity: Critical, Priority: Low — vì khách hàng có thể dùng chuyển khoản thủ công thay thế</v>
+      </c>
+      <c r="F14" t="str">
         <v>Severity: Critical (Nghiêm trọng), Priority: High (Ưu tiên cao) — lỗi chặn chức năng cốt lõi của dự án và làm hỏng trải nghiệm người dùng ngay lập tức</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Severity: Low, Priority: High — vì giao diện nút thanh toán vẫn hiển thị rất đẹp mắt</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Severity: Critical, Priority: Low — vì khách hàng có thể dùng chuyển khoản thủ công thay thế</v>
       </c>
       <c r="H14" t="str">
         <v>Severity: Medium, Priority: Medium — lỗi ở mức trung bình vì ứng dụng vẫn mở lại được</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Kiểm thử chuyển trạng thái giúp bao phủ đầy đủ các luồng chuyển dịch trạng thái hợp lệ và phát hiện các luồng chuyển dịch sai logic (ví dụ: Đơn hàng đã hủy không được phép chuyển sang Đang giao).</v>
       </c>
       <c r="E15" t="str">
+        <v>Hệ thống kho báo cáo tĩnh chỉ hiển thị dữ liệu thô dạng bảng của doanh nghiệp</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Hệ thống landing page giới thiệu sản phẩm chỉ chứa văn bản thô và hình ảnh quảng cáo</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Các ứng dụng tính toán công thức toán học độc lập không lưu trữ dữ liệu</v>
+      </c>
+      <c r="H15" t="str">
         <v>Hệ thống có các đối tượng thay đổi trạng thái tuần tự dựa trên các sự kiện kích hoạt cụ thể (ví dụ: Vòng đời đơn hàng từ Chờ duyệt -&gt; Đang giao -&gt; Thành công)</v>
       </c>
-      <c r="F15" t="str">
-        <v>Hệ thống kho báo cáo tĩnh chỉ hiển thị dữ liệu thô dạng bảng của doanh nghiệp</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Hệ thống landing page giới thiệu sản phẩm chỉ chứa văn bản thô và hình ảnh quảng cáo</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Các ứng dụng tính toán công thức toán học độc lập không lưu trữ dữ liệu</v>
-      </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -888,19 +888,19 @@
         <v>Nguyên lý "Kiểm thử sớm" (Early Testing) giúp giảm thiểu chi phí sửa lỗi. Phát hiện lỗi logic trên tài liệu yêu cầu (SRS) rẻ hơn gấp hàng chục lần so với sửa lỗi sau khi dev đã code xong.</v>
       </c>
       <c r="E17" t="str">
+        <v>Bắt đầu sau khi khách hàng đã thực hiện xong kiểm thử chấp nhận UAT trên Production</v>
+      </c>
+      <c r="F17" t="str">
         <v>Bắt đầu ngay từ giai đoạn khơi gợi và phân tích yêu cầu (Early Testing) — review tài liệu yêu cầu cùng BA để phát hiện sớm các lỗi logic nghiệp vụ trước khi code</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>Bắt đầu khi lập trình viên đã hoàn thành 100% mã nguồn và bàn giao toàn bộ hệ thống sang QA</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Bắt đầu sau khi khách hàng đã thực hiện xong kiểm thử chấp nhận UAT trên Production</v>
       </c>
       <c r="H17" t="str">
         <v>Bắt đầu vào ngày cuối cùng của Sprint phát triển để kiểm tra nhanh giao diện ứng dụng</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -920,10 +920,10 @@
         <v>Để cung cấp tiêu chuẩn so sánh khách quan với kết quả thực tế khi chạy test, giúp xác định chính xác ca kiểm thử đó Pass hay Fail</v>
       </c>
       <c r="F18" t="str">
+        <v>Để tự động hóa việc tính toán thời gian phản hồi của máy chủ ứng dụng di động</v>
+      </c>
+      <c r="G18" t="str">
         <v>Để hướng dẫn lập trình viên cách viết các câu lệnh điều kiện rẽ nhánh trong code</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Để tự động hóa việc tính toán thời gian phản hồi của máy chủ ứng dụng di động</v>
       </c>
       <c r="H18" t="str">
         <v>Để hiển thị thông tin hướng dẫn sử dụng sản phẩm cho người dùng cuối</v>
@@ -952,10 +952,10 @@
         <v>Đặt Ngày đến = Hiện tại + 10 ngày; Ngày đi = Hiện tại + 20 ngày — kiểm tra một kịch bản thành công ngẫu nhiên</v>
       </c>
       <c r="G19" t="str">
+        <v>Đặt Ngày đến và Ngày đi cách nhau đúng một năm để kiểm tra khả năng xử lý năm nhuận của hệ thống</v>
+      </c>
+      <c r="H19" t="str">
         <v>Đặt Ngày đến = Hiện tại - 5 ngày; Ngày đi = Hiện tại - 2 ngày — kiểm tra kịch bản thất bại xa biên</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Đặt Ngày đến và Ngày đi cách nhau đúng một năm để kiểm tra khả năng xử lý năm nhuận của hệ thống</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>QA cần chủ động quản lý rủi ro bằng cách kiểm thử dựa trên độ ưu tiên (Risk-based testing), tập trung vào Happy Path và Core flows để đảm bảo chất lượng tối thiểu trước khi release.</v>
       </c>
       <c r="E20" t="str">
+        <v>Ký duyệt nghiệm thu Pass tất cả các tính năng để kịp tiến độ bàn giao sprint của team phát triển</v>
+      </c>
+      <c r="F20" t="str">
         <v>Báo cáo ngay với Scrum Master/PM về rủi ro trễ hạn, ưu tiên thực hiện Smoke Test và các Test Case mức độ ưu tiên cao (High Priority) của các tính năng cốt lõi; chuyển các phần kiểm thử sâu sang Sprint sau — quản lý rủi ro phạm vi</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
+        <v>Từ chối kiểm thử bản build này và yêu cầu hủy bỏ toàn bộ kết quả của Sprint hiện tại</v>
+      </c>
+      <c r="H20" t="str">
         <v>Chấp nhận làm thêm giờ xuyên đêm để chạy hết 100% test case chi tiết đã viết mà không cần báo cáo rủi ro</v>
       </c>
-      <c r="G20" t="str">
-        <v>Ký duyệt nghiệm thu Pass tất cả các tính năng để kịp tiến độ bàn giao sprint của team phát triển</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Từ chối kiểm thử bản build này và yêu cầu hủy bỏ toàn bộ kết quả của Sprint hiện tại</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Decision Table cho 3 điều kiện nhị phân (T/F) sẽ có 8 tổ hợp quy tắc. Việc kiểm thử đầy đủ 8 trường hợp này đảm bảo hệ thống không bị lỗi logic chéo khi tính toán giá tiền đơn hàng.</v>
       </c>
       <c r="E21" t="str">
+        <v>Viết 2 test case: 1 case cho khách thường mua đơn nhỏ; 1 case cho khách VIP mua đơn lớn có mã KM</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Thiết kế 1 test case duy nhất chứa đầy đủ tất cả các điều kiện đều đúng (True) để tiết kiệm thời gian</v>
+      </c>
+      <c r="G21" t="str">
         <v>Xác định 3 điều kiện (Giỏ hàng &gt;= 1M, Khách VIP, Có mã KM) tạo thành 2^3 = 8 cột quy tắc (Rules) kiểm thử độc lập — bao phủ toàn bộ tổ hợp logic</v>
       </c>
-      <c r="F21" t="str">
+      <c r="H21" t="str">
         <v>Chỉ viết 3 test case tương ứng với 3 điều kiện độc lập chạy riêng lẻ</v>
       </c>
-      <c r="G21" t="str">
-        <v>Thiết kế 1 test case duy nhất chứa đầy đủ tất cả các điều kiện đều đúng (True) để tiết kiệm thời gian</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Viết 2 test case: 1 case cho khách thường mua đơn nhỏ; 1 case cho khách VIP mua đơn lớn có mã KM</v>
-      </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Nghịch lý thuốc trừ sâu xảy ra vì phần mềm tiến hóa và các bug cũ đã được sửa. QA cần cập nhật kịch bản test để thích ứng với các thay đổi nghiệp vụ và kỹ thuật mới.</v>
       </c>
       <c r="E22" t="str">
-        <v>Nếu chạy đi chạy lại một bộ test case cũ thì sau một thời gian sẽ không tìm thêm được bug mới. Khắc phục: Phải thường xuyên rà soát, cập nhật và viết thêm các test case mới để bao phủ các kịch bản khác</v>
+        <v>Nếu phần mềm có quá nhiều bug thì các bug này sẽ tự động triệt tiêu lẫn nhau khi chạy code</v>
       </c>
       <c r="F22" t="str">
-        <v>Nếu phần mềm có quá nhiều bug thì các bug này sẽ tự động triệt tiêu lẫn nhau khi chạy code</v>
+        <v>Lập trình viên khi thấy QA viết quá nhiều test case sẽ tự động tăng cường chất lượng code tự viết</v>
       </c>
       <c r="G22" t="str">
         <v>Kiểm thử tự động chạy liên tục sẽ sinh ra các lỗi giả (false bugs) làm tốn tài nguyên hệ thống</v>
       </c>
       <c r="H22" t="str">
-        <v>Lập trình viên khi thấy QA viết quá nhiều test case sẽ tự động tăng cường chất lượng code tự viết</v>
+        <v>Nếu chạy đi chạy lại một bộ test case cũ thì sau một thời gian sẽ không tìm thêm được bug mới. Khắc phục: Phải thường xuyên rà soát, cập nhật và viết thêm các test case mới để bao phủ các kịch bản khác</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1065,13 +1065,13 @@
         <v>Sử dụng các công cụ giám sát mạng (Network logs/DevTools) hoặc log server để phân tích Request/Response; xác định chính xác API gửi đi có đúng format và Response trả về bị lỗi gì trước khi gán bug — kiểm chứng bằng dữ liệu</v>
       </c>
       <c r="F23" t="str">
+        <v>Gửi email trực tiếp cho nhà cung cấp dịch vụ bên thứ ba yêu cầu họ sửa lỗi mà không cần kiểm tra log</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Đóng lỗi đó lại và đánh dấu là lỗi không thể tái hiện (Cannot reproduce) để tránh mất thời gian</v>
+      </c>
+      <c r="H23" t="str">
         <v>Gán ngay lỗi đó cho lập trình viên Backend của đội mình tự kiểm tra và tự tìm nguyên nhân</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Gửi email trực tiếp cho nhà cung cấp dịch vụ bên thứ ba yêu cầu họ sửa lỗi mà không cần kiểm tra log</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Đóng lỗi đó lại và đánh dấu là lỗi không thể tái hiện (Cannot reproduce) để tránh mất thời gian</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1091,10 +1091,10 @@
         <v>Flaky Tests thường do bất đồng bộ (timing issues), dữ liệu test không ổn định, hoặc môi trường mạng chập chờn. Nó làm giảm giá trị của CI/CD vì kết quả không đáng tin cậy.</v>
       </c>
       <c r="E24" t="str">
+        <v>Là kịch bản test tự động chạy quá nhanh dẫn đến crash máy chủ cơ sở dữ liệu</v>
+      </c>
+      <c r="F24" t="str">
         <v>Là test case lúc Pass lúc Fail trên cùng một phiên bản code mà không có sự thay đổi nào; gây mất niềm tin vào kết quả kiểm thử tự động và tốn thời gian debug giả</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Là kịch bản test tự động chạy quá nhanh dẫn đến crash máy chủ cơ sở dữ liệu</v>
       </c>
       <c r="G24" t="str">
         <v>Là các test case tự động viết bằng ngôn ngữ Python nhưng chạy trên máy chủ chạy hệ điều hành Windows</v>
@@ -1103,7 +1103,7 @@
         <v>Là lỗi phát sinh do compiler không biên dịch được mã nguồn kiểm thử tự động</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Suspension Criteria giúp bảo vệ tài nguyên dự án. Nếu bản build quá lỗi (blocker/crash liên tục), việc cố gắng test tiếp sẽ vô ích và lãng phí thời gian của QA.</v>
       </c>
       <c r="E25" t="str">
+        <v>Các quy định về việc lập trình viên không được phép commit code mới sau 18 giờ hàng ngày</v>
+      </c>
+      <c r="F25" t="str">
         <v>Các điều kiện mà khi xảy ra, hoạt động kiểm thử bắt buộc phải tạm dừng ngay lập tức (ví dụ: Bản build bị crash ngay khi mở ứng dụng, hoặc có quá nhiều lỗi blocker)</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Mức lương tối thiểu cần chi trả cho đội ngũ kiểm thử viên để họ đồng ý tiếp tục làm việc</v>
       </c>
       <c r="G25" t="str">
         <v>Thời điểm mà dự án chính thức hết ngân sách phát triển và phải bàn giao cho khách hàng</v>
       </c>
       <c r="H25" t="str">
-        <v>Các quy định về việc lập trình viên không được phép commit code mới sau 18 giờ hàng ngày</v>
+        <v>Mức lương tối thiểu cần chi trả cho đội ngũ kiểm thử viên để họ đồng ý tiếp tục làm việc</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Để kiểm tra tính đúng đắn của máy trạng thái (State Machine), ta cần kiểm tra từng bước chuyển: (Active + Sai 1 -&gt; Active), (Active + Sai 2 -&gt; Active), (Active + Sai 3 -&gt; Blocked) để đảm bảo bộ đếm hoạt động chính xác.</v>
       </c>
       <c r="E26" t="str">
+        <v>4 ca kiểm thử để bao phủ cả trường hợp nhập đúng ở lần thứ 2</v>
+      </c>
+      <c r="F26" t="str">
         <v>3 ca kiểm thử liên tục để mô tả quá trình chuyển dịch trạng thái từ Active sang Blocked qua từng bước sai sót</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>1 ca kiểm thử duy nhất nhập sai PIN 3 lần liên tiếp để kiểm tra trạng thái khóa cuối cùng</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>2 ca kiểm thử độc lập: 1 case nhập sai 1 lần; 1 case nhập sai 3 lần</v>
       </c>
-      <c r="H26" t="str">
-        <v>4 ca kiểm thử để bao phủ cả trường hợp nhập đúng ở lần thứ 2</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
